--- a/results/Int Task Remove ACC -0.3/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_4_permute.xlsx
@@ -440,207 +440,207 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7738968936876958</v>
+        <v>0.8089926602115625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7762979739941658</v>
+        <v>0.794872029821978</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.771494376038929</v>
+        <v>0.758944221776167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7723804975647828</v>
+        <v>0.7559443087353759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7739583400708754</v>
+        <v>0.7559443087353759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7638480743565916</v>
+        <v>0.7484309612154741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7616670870892883</v>
+        <v>0.7533260100743322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7588658866210023</v>
+        <v>0.7571820401205356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7587000532535321</v>
+        <v>0.7469702621065545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7532361761807946</v>
+        <v>0.6917838639641757</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7595276030807995</v>
+        <v>0.7106852745000385</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7201983244900849</v>
+        <v>0.70898310188529</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7243087641227863</v>
+        <v>0.7092989578549679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7209958697969108</v>
+        <v>0.6884080859128238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7106983902484949</v>
+        <v>0.6867016012711855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7288694512298979</v>
+        <v>0.6955484431067579</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7367987296768783</v>
+        <v>0.6752235246939</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7375262045467448</v>
+        <v>0.6640084817568922</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7306059403919776</v>
+        <v>0.6262286581619123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7284592696720056</v>
+        <v>0.6255326251547838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.736261343325737</v>
+        <v>0.6210720130050731</v>
       </c>
     </row>
     <row r="23">
@@ -650,277 +650,277 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7254536072620282</v>
+        <v>0.6259142395345311</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7206543213336811</v>
+        <v>0.6164656902800446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7099351614890004</v>
+        <v>0.600967187631382</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7116416461306386</v>
+        <v>0.6063067345954636</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6675173936384667</v>
+        <v>0.6079803400320671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6827586120160378</v>
+        <v>0.6125280910585091</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6832945610248825</v>
+        <v>0.6167299815948319</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6849367245987479</v>
+        <v>0.6118020535309392</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6742590680128815</v>
+        <v>0.6124652073330329</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6752066359219149</v>
+        <v>0.6210547648975139</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6644360910901307</v>
+        <v>0.6029194578057389</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6691624318969254</v>
+        <v>0.5997623354512572</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6747549511052084</v>
+        <v>0.5976471065940234</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6518244904441891</v>
+        <v>0.5987533211590441</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6224868968282886</v>
+        <v>0.5944314125409553</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.606779799878832</v>
+        <v>0.5930035926370704</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5898707254338438</v>
+        <v>0.5936038627136879</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5951903292735601</v>
+        <v>0.5936038627136879</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5997366429577055</v>
+        <v>0.6015874008323649</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6187081239305275</v>
+        <v>0.5929664014051459</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.60095011919161</v>
+        <v>0.5808208589988767</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5632545597887681</v>
+        <v>0.5798732910898432</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5629701456818285</v>
+        <v>0.5798732910898432</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5626857315748888</v>
+        <v>0.5832862603731197</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5471629737749711</v>
+        <v>0.5818327479756831</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5262392226277923</v>
+        <v>0.5805693240969717</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5322363536925683</v>
+        <v>0.5769333870899352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5410860702127338</v>
+        <v>0.5798404118848085</v>
       </c>
     </row>
     <row r="51">
@@ -930,47 +930,47 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5371285278668331</v>
+        <v>0.5766146564356642</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5147841435272523</v>
+        <v>0.5810709565584851</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5074193812672616</v>
+        <v>0.5869221973801562</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4771742856588453</v>
+        <v>0.5762087869046618</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4867999873513877</v>
+        <v>0.560913308855394</v>
       </c>
     </row>
     <row r="56">
@@ -980,347 +980,347 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4861682754120321</v>
+        <v>0.5595226801834337</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4861682754120321</v>
+        <v>0.5517220438719989</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.470749904596405</v>
+        <v>0.5522608675654368</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4723877561433806</v>
+        <v>0.5522608675654368</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4864798193548202</v>
+        <v>0.5489150940345264</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.498133611027865</v>
+        <v>0.5582278144419842</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5155728851125115</v>
+        <v>0.5587308842457942</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5157000899057607</v>
+        <v>0.5607546621994068</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5140564889895987</v>
+        <v>0.5363821878793236</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5148782894476797</v>
+        <v>0.5335066049471885</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5085582953695299</v>
+        <v>0.5427064939843631</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5089699142697187</v>
+        <v>0.5393679071649358</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5089699142697187</v>
+        <v>0.5352660915860138</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5089699142697187</v>
+        <v>0.5233020136446904</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5065359547582139</v>
+        <v>0.5236178696143682</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5027142412593418</v>
+        <v>0.5208337375858543</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5027142412593418</v>
+        <v>0.5208337375858543</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4808429222031295</v>
+        <v>0.5205807653416527</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4705183128188654</v>
+        <v>0.5210867098300559</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4705183128188654</v>
+        <v>0.5314842643358724</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.475524935373497</v>
+        <v>0.5294304818618182</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.498710883627737</v>
+        <v>0.5294304818618182</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4989609811873453</v>
+        <v>0.5268364383520295</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5006031447612107</v>
+        <v>0.5182696985965071</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.500318730654271</v>
+        <v>0.5151411434201704</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.500318730654271</v>
+        <v>0.5094528612813762</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5000972002728076</v>
+        <v>0.5116352858909762</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.506701608457897</v>
+        <v>0.5116352858909762</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5072389948090383</v>
+        <v>0.511603844028238</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5030371042727155</v>
+        <v>0.5153641111439304</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.503984672181749</v>
+        <v>0.5115767141923897</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5002229677237601</v>
+        <v>0.5071933591911212</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5001600839982838</v>
+        <v>0.5190830546685956</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5004444981052235</v>
+        <v>0.5262334732586059</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5008232378003776</v>
+        <v>0.5032686960502553</v>
       </c>
     </row>
   </sheetData>
